--- a/docs/test-cases/SPM-42_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-42_Test_Cases.xlsx
@@ -7,24 +7,23 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC01" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC02" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC03" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC04" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC05" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC06" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC07" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC08" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC09" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC10" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC11" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC12" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC13" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC14" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC15" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC16" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC17" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC01" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC02" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC03" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC04" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC05" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC06" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC07" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC08" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC09" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC11" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC12" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC13" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC14" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC15" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC16" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC17" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1370,11 +1369,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.5" customHeight="1">
+          <t>SPM-42-TC09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1382,12 +1381,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42 (so Day 2 has no request yet).
-Logged in as Daniel Tan, assigned to spm42_three_sessions 'SPM42 Three-Session Forum' (Day 2: 2 Mar 2027 (2026-09-26 + 157) 14:00-17:00) and to 'SPM42 Refusal Checks' (7 Mar 2027 09:00-17:00, no sessions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="152.5" customHeight="1">
+          <t>Run npm run fixtures:spm42.
+Logged in as Daniel Tan, assigned to spm42_three_sessions 'SPM42 Three-Session Forum' (status Approved; opening the Venue tab moves it to Planning, SPM-40). Sessions: 'Day 1' 1 Mar 2027 (2026-09-26 + 156) 09:00-12:00, expects 80, Theatre; 'Day 2' 2 Mar 2027 (2026-09-26 + 157) 14:00-17:00, expects 30, Classroom; 'Day 3' 3 Mar 2027 (2026-09-26 + 158) 19:00-22:00, expects 60, Banquet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="166" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1395,15 +1394,16 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open 'SPM42 Three-Session Forum', open the Venue tab, choose Session 'Day 2' and click 'Request booking' on 'Orchard Studio (ORC-STU)'
-2. Tick only 'AM (07:00–12:00)' for 2 Mar 2027 and click 'Submit request'
-3. Change the date to 1 Mar 2027, tick only 'PM (13:00–18:00)' and click 'Submit request'
-4. Open 'SPM42 Refusal Checks', open the Venue tab and click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)'
-5. Tick only 'AM (07:00–12:00)' for 7 Mar 2027 and click 'Submit request'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
+          <t>1. Open the event 'SPM42 Three-Session Forum'
+2. Open the Venue tab (Find a venue)
+3. Choose Session 'Day 1', click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)', check the date and slot shown, click 'Submit request'
+4. Choose Session 'Day 2', click 'Request booking' on 'Orchard Studio (ORC-STU)', check the date and slot shown, click 'Submit request'
+5. Choose Session 'Day 3', click 'Request booking' on 'Orchard Gallery (ORC-GAL)', check the date and slot shown, click 'Submit request'
+6. Look at the event's booking requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1411,13 +1411,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Attempt 1: Day 2, 2 Mar 2027 AM (session runs in PM)
-Attempt 2: Day 2, 1 Mar 2027 PM (Day 1's date)
-Attempt 3: SPM42 Refusal Checks, 7 Mar 2027 AM only (event runs into PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+          <t>Day 1: Orchard Seminar Room, 1 Mar 2027, AM
+Day 2: Orchard Studio, 2 Mar 2027, PM
+Day 3: Orchard Gallery, 3 Mar 2027, Night</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1425,9 +1425,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Attempts 1 and 2 show 'The chosen slots do not cover the session's time (2 Mar 2027, 14:00–17:00).'
-Attempt 3 shows 'The chosen slots do not cover the event's time (7 Mar 2027, 09:00–17:00).'
-No request is created.</t>
+          <t>Each screen opens on its own session's date with its slot already ticked: Day 1 → 1 Mar 2027 AM; Day 2 → 2 Mar 2027 PM; Day 3 → 3 Mar 2027 Night.
+Three separate requests are listed, each labelled with its session and showing that session's layout: Day 1 Theatre, Day 2 Classroom, Day 3 Banquet.</t>
         </is>
       </c>
     </row>
@@ -1536,11 +1535,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="112" customHeight="1">
+          <t>SPM-42-TC10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1548,12 +1547,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
-Logged in as Daniel Tan, assigned to spm42_three_sessions 'SPM42 Three-Session Forum' (status Approved; opening the Venue tab moves it to Planning, SPM-40). Sessions: 'Day 1' 1 Mar 2027 (2026-09-26 + 156) 09:00-12:00, expects 80, Theatre; 'Day 2' 2 Mar 2027 (2026-09-26 + 157) 14:00-17:00, expects 30, Classroom; 'Day 3' 3 Mar 2027 (2026-09-26 + 158) 19:00-22:00, expects 60, Banquet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="166" customHeight="1">
+          <t>TC04 and TC09 have been run.
+Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1561,16 +1560,14 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Three-Session Forum'
-2. Open the Venue tab (Find a venue)
-3. Choose Session 'Day 1', click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)', check the date and slot shown, click 'Submit request'
-4. Choose Session 'Day 2', click 'Request booking' on 'Orchard Studio (ORC-STU)', check the date and slot shown, click 'Submit request'
-5. Choose Session 'Day 3', click 'Request booking' on 'Orchard Gallery (ORC-GAL)', check the date and slot shown, click 'Submit request'
-6. Look at the event's booking requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>1. Click 'Booking Requests' in the sidebar
+2. Find the request for Orchard Seminar Room on 6 Mar 2027
+3. Find the request for Orchard Studio on 2 Mar 2027
+4. Click the event reference on one of them</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1578,13 +1575,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Day 1: Orchard Seminar Room, 1 Mar 2027, AM
-Day 2: Orchard Studio, 2 Mar 2027, PM
-Day 3: Orchard Gallery, 3 Mar 2027, Night</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1">
+          <t>Requests: SPM42 Town Hall (no sessions); SPM42 Three-Session Forum, Day 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1592,8 +1587,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Each screen opens on its own session's date with its slot already ticked: Day 1 → 1 Mar 2027 AM; Day 2 → 2 Mar 2027 PM; Day 3 → 3 Mar 2027 Night.
-Three separate requests are listed, each labelled with its session and showing that session's layout: Day 1 Theatre, Day 2 Classroom, Day 3 Banquet.</t>
+          <t>The 6 Mar request shows the event reference (EVT-…) and title 'SPM42 Town Hall', with no session.
+The 2 Mar request shows 'SPM42 Three-Session Forum' and session 'Day 2'.
+Clicking an event reference opens that event.</t>
         </is>
       </c>
     </row>
@@ -1702,11 +1698,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.5" customHeight="1">
+          <t>SPM-42-TC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1714,8 +1710,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>TC04 and TC09 have been run.
-Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).</t>
+          <t>TC04 has been run.</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1722,8 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Booking Requests' in the sidebar
-2. Find the request for Orchard Seminar Room on 6 Mar 2027
-3. Find the request for Orchard Studio on 2 Mar 2027
-4. Click the event reference on one of them</t>
+          <t>1. As Daniel Tan, open 'SPM42 Town Hall', open the Venue tab and look at its booking requests
+2. Log in as Venue Staff Marcus Wong and click 'Booking Requests' in the sidebar</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1735,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Requests: SPM42 Town Hall (no sessions); SPM42 Three-Session Forum, Day 2</t>
+          <t>Request: SPM42 Town Hall, Orchard Seminar Room, 6 Mar 2027, AM + PM</t>
         </is>
       </c>
     </row>
@@ -1754,9 +1747,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The 6 Mar request shows the event reference (EVT-…) and title 'SPM42 Town Hall', with no session.
-The 2 Mar request shows 'SPM42 Three-Session Forum' and session 'Day 2'.
-Clicking an event reference opens that event.</t>
+          <t>Both screens show the request with the status badge 'Pending'.
+Marcus Wong's list shows venue Orchard Seminar Room, 6 Mar 2027, AM and PM, setup 5 Mar 2027 Night, turnaround 6 Mar 2027 Night, requested by Daniel Tan.</t>
         </is>
       </c>
     </row>
@@ -1865,11 +1857,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC11</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17.5" customHeight="1">
+          <t>SPM-42-TC12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1877,11 +1869,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>TC04 has been run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
+          <t>Seeded data: 'Town Hall Q4' (status Planning) is assigned to Daniel Tan.
+Accounts (password123): Coordinator Priya Raj (priya.raj@connectsphere.com), Organiser Rachel Ng (rachel.ng@meridianfina.com, organiser of 'Town Hall Q4'), Ops Manager Grace Lim (grace.lim@connectsphere.com), Venue Staff Marcus Wong (marcus.wong@connectsphere.com), Technical Support Kenji Sato (kenji.sato@connectsphere.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1889,12 +1882,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. As Daniel Tan, open 'SPM42 Town Hall', open the Venue tab and look at its booking requests
-2. Log in as Venue Staff Marcus Wong and click 'Booking Requests' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+          <t>1. Log in as each account in turn
+2. Open the event 'Town Hall Q4'
+3. Open the Venue tab if it is shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1902,11 +1896,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Request: SPM42 Town Hall, Orchard Seminar Room, 6 Mar 2027, AM + PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+          <t>Accounts: Priya Raj (Coordinator, not assigned), Rachel Ng (Organiser), Grace Lim (Ops Manager), Marcus Wong (Venue Staff), Kenji Sato (Technical Support)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1914,8 +1908,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Both screens show the request with the status badge 'Pending'.
-Marcus Wong's list shows venue Orchard Seminar Room, 6 Mar 2027, AM and PM, setup 5 Mar 2027 Night, turnaround 6 Mar 2027 Night, requested by Daniel Tan.</t>
+          <t>None of the five sees a 'Request booking' button anywhere for this event.
+Priya Raj's Venue tab says 'Only the assigned Coordinator can request a venue booking.'</t>
         </is>
       </c>
     </row>
@@ -2024,11 +2018,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="112" customHeight="1">
+          <t>SPM-42-TC13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2036,12 +2030,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Seeded data: 'Town Hall Q4' (status Planning) is assigned to Daniel Tan.
-Accounts (password123): Coordinator Priya Raj (priya.raj@connectsphere.com), Organiser Rachel Ng (rachel.ng@meridianfina.com, organiser of 'Town Hall Q4'), Ops Manager Grace Lim (grace.lim@connectsphere.com), Venue Staff Marcus Wong (marcus.wong@connectsphere.com), Technical Support Kenji Sato (kenji.sato@connectsphere.com).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>Seeded data.
+Logged in as Coordinator Priya Raj (priya.raj@connectsphere.com / password123), assigned to 'Kirana Regional Managers Offsite' (status Under review, 22 Nov 2026 (2026-09-26 + 57) 09:00-17:00).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2049,13 +2043,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Log in as each account in turn
-2. Open the event 'Town Hall Q4'
-3. Open the Venue tab if it is shown</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>1. Open the event 'Kirana Regional Managers Offsite'
+2. Open the Venue tab (Find a venue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2063,11 +2056,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Accounts: Priya Raj (Coordinator, not assigned), Rachel Ng (Organiser), Grace Lim (Ops Manager), Marcus Wong (Venue Staff), Kenji Sato (Technical Support)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>Event status: Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2075,8 +2068,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>None of the five sees a 'Request booking' button anywhere for this event.
-Priya Raj's Venue tab says 'Only the assigned Coordinator can request a venue booking.'</t>
+          <t>No 'Request booking' button is shown.
+The page says 'A venue booking can only be requested once the event is Approved or in Planning.'</t>
         </is>
       </c>
     </row>
@@ -2185,11 +2178,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.5" customHeight="1">
+          <t>SPM-42-TC14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="139" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2197,12 +2190,15 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Seeded data.
-Logged in as Coordinator Priya Raj (priya.raj@connectsphere.com / password123), assigned to 'Kirana Regional Managers Offsite' (status Under review, 22 Nov 2026 (2026-09-26 + 57) 09:00-17:00).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31" customHeight="1">
+          <t>Run npm run fixtures:spm42. Seeded data, unchanged:
+- 'Product Showcase' has an Approved booking at Marina Auditorium (MAR-AUD), 21 Oct 2026 (2026-09-26 + 25) 11:00-15:00.
+- 'Pearl Delta Safety Conference' has a Pending booking at Changi Conference Centre (CBP-CONF), 14 Dec 2026 (2026-09-26 + 79) 09:00-17:00.
+- Marina Auditorium is unavailable for maintenance 20-21 Nov 2026 (2026-09-26 + 55 to + 56).
+Logged in as Daniel Tan, assigned to the three events in Test data (status Planning, no sessions, no booking).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2210,12 +2206,16 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'Kirana Regional Managers Offsite'
-2. Open the Venue tab (Find a venue)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
+          <t>1. Open the event
+2. Open the Venue tab (Find a venue)
+3. Click 'Request booking' on the venue
+4. Tick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' for the date
+5. Click 'Submit request'
+6. Repeat for the next event</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="85" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2223,11 +2223,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event status: Under review</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>1. spm42_clash_check 'SPM42 Clash Check', 21 Oct 2026 11:00-15:00, Marina Auditorium (Approved booking)
+2. 'Staff Retreat', 14 Dec 2026 09:00-17:00, Changi Conference Centre (Pending hold)
+3. 'Sports Meet', 20 Nov 2026 09:00-17:00, Marina Auditorium (maintenance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2235,8 +2237,10 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>No 'Request booking' button is shown.
-The page says 'A venue booking can only be requested once the event is Approved or in Planning.'</t>
+          <t>1. 'Marina Auditorium is already booked for this time.'
+2. 'Changi Conference Centre is on hold for another event at this time.'
+3. 'Marina Auditorium is unavailable at this time.'
+No request is created for any of the three.</t>
         </is>
       </c>
     </row>
@@ -2345,11 +2349,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="139" customHeight="1">
+          <t>SPM-42-TC15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2357,15 +2361,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42. Seeded data, unchanged:
-- 'Product Showcase' has an Approved booking at Marina Auditorium (MAR-AUD), 21 Oct 2026 (2026-09-26 + 25) 11:00-15:00.
-- 'Pearl Delta Safety Conference' has a Pending booking at Changi Conference Centre (CBP-CONF), 14 Dec 2026 (2026-09-26 + 79) 09:00-17:00.
-- Marina Auditorium is unavailable for maintenance 20-21 Nov 2026 (2026-09-26 + 55 to + 56).
-Logged in as Daniel Tan, assigned to the three events in Test data (status Planning, no sessions, no booking).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.5" customHeight="1">
+          <t>Seeded data: 'Product Showcase' has an Approved booking at Marina Auditorium (MAR-AUD, setup 60 min, teardown 30 min) on 21 Oct 2026 AM + PM, so its setup holds 20 Oct 2026 Night.
+Logged in as Daniel Tan, assigned to 'Keynote Rehearsal' (status Planning, 20 Oct 2026 (2026-09-26 + 24) 14:00-16:00, no sessions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2373,16 +2374,15 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event
+          <t>1. Open the event 'Keynote Rehearsal'
 2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on the venue
-4. Tick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' for the date
-5. Click 'Submit request'
-6. Repeat for the next event</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="85" customHeight="1">
+3. Click 'Request booking' on 'Marina Auditorium (MAR-AUD)'
+4. Tick only 'PM (13:00–18:00)' for 20 Oct 2026
+5. Click 'Submit request'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2390,13 +2390,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. spm42_clash_check 'SPM42 Clash Check', 21 Oct 2026 11:00-15:00, Marina Auditorium (Approved booking)
-2. 'Staff Retreat', 14 Dec 2026 09:00-17:00, Changi Conference Centre (Pending hold)
-3. 'Sports Meet', 20 Nov 2026 09:00-17:00, Marina Auditorium (maintenance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+          <t>Requested: 20 Oct 2026 PM (its turnaround takes 20 Oct Night)
+Existing: Product Showcase, 21 Oct AM + PM (its setup takes 20 Oct Night)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2404,10 +2403,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>1. 'Marina Auditorium is already booked for this time.'
-2. 'Changi Conference Centre is on hold for another event at this time.'
-3. 'Marina Auditorium is unavailable at this time.'
-No request is created for any of the three.</t>
+          <t>Error 'Marina Auditorium is already booked for this time.' is shown, although the two events' own slots (20 Oct PM and 21 Oct AM + PM) do not overlap.
+No request is created.</t>
         </is>
       </c>
     </row>
@@ -2516,11 +2513,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="85" customHeight="1">
+          <t>SPM-42-TC16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="139" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2528,12 +2525,14 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Seeded data: 'Product Showcase' has an Approved booking at Marina Auditorium (MAR-AUD, setup 60 min, teardown 30 min) on 21 Oct 2026 AM + PM, so its setup holds 20 Oct 2026 Night.
-Logged in as Daniel Tan, assigned to 'Keynote Rehearsal' (status Planning, 20 Oct 2026 (2026-09-26 + 24) 14:00-16:00, no sessions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
+          <t>Run npm run fixtures:spm42. It creates:
+- 'SPM42 Cancelled Hold' with a Cancelled booking at Orchard Gallery (ORC-GAL), 15 Mar 2027 (2026-09-26 + 170) 09:00-17:00.
+- 'SPM42 Rejected Hold' with a Rejected booking at Marina Auditorium (MAR-AUD), 16 Mar 2027 (2026-09-26 + 171) 09:00-18:00 — had it been approved, its turnaround would hold 16 Mar Night.
+Logged in as Daniel Tan, assigned to the two events in Test data (status Planning, no sessions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2541,15 +2540,16 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'Keynote Rehearsal'
+          <t>1. Open the event
 2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on 'Marina Auditorium (MAR-AUD)'
-4. Tick only 'PM (13:00–18:00)' for 20 Oct 2026
-5. Click 'Submit request'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
+3. Click 'Request booking' on the venue
+4. Tick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' for the date
+5. Click 'Submit request'
+6. Repeat for the next event</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="85" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Requested: 20 Oct 2026 PM (its turnaround takes 20 Oct Night)
-Existing: Product Showcase, 21 Oct AM + PM (its setup takes 20 Oct Night)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>1. spm42_after_cancel 'SPM42 After Cancellation', 15 Mar 2027 10:00-16:00, Orchard Gallery (same slots as the cancelled booking)
+2. spm42_after_reject 'SPM42 After Rejection', 17 Mar 2027 (2026-09-26 + 172) 10:00-16:00, Marina Auditorium (its setup takes 16 Mar Night)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2570,8 +2570,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Error 'Marina Auditorium is already booked for this time.' is shown, although the two events' own slots (20 Oct PM and 21 Oct AM + PM) do not overlap.
-No request is created.</t>
+          <t>Both show 'Booking request sent to Venue Staff.' and the request is Pending.</t>
         </is>
       </c>
     </row>
@@ -2680,11 +2679,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="139" customHeight="1">
+          <t>SPM-42-TC17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2692,10 +2691,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42. It creates:
-- 'SPM42 Cancelled Hold' with a Cancelled booking at Orchard Gallery (ORC-GAL), 15 Mar 2027 (2026-09-26 + 170) 09:00-17:00.
-- 'SPM42 Rejected Hold' with a Rejected booking at Marina Auditorium (MAR-AUD), 16 Mar 2027 (2026-09-26 + 171) 09:00-18:00 — had it been approved, its turnaround would hold 16 Mar Night.
-Logged in as Daniel Tan, assigned to the two events in Test data (status Planning, no sessions).</t>
+          <t>TC04 and TC09 have been run (SPM42 Town Hall and Session 'Day 1' each have a Pending request).
+Logged in as Daniel Tan.</t>
         </is>
       </c>
     </row>
@@ -2708,15 +2705,14 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Open the event
-2. Open the Venue tab (Find a venue)
+2. Open the Venue tab (Find a venue), choosing the session where there is one
 3. Click 'Request booking' on the venue
-4. Tick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' for the date
-5. Click 'Submit request'
-6. Repeat for the next event</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="85" customHeight="1">
+4. Click 'Submit request' with the date and slots already filled in
+5. Repeat for the next attempt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2724,12 +2720,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. spm42_after_cancel 'SPM42 After Cancellation', 15 Mar 2027 10:00-16:00, Orchard Gallery (same slots as the cancelled booking)
-2. spm42_after_reject 'SPM42 After Rejection', 17 Mar 2027 (2026-09-26 + 172) 10:00-16:00, Marina Auditorium (its setup takes 16 Mar Night)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
+          <t>1. SPM42 Town Hall, Orchard Studio (ORC-STU), 6 Mar 2027 AM + PM
+2. SPM42 Three-Session Forum, Session 'Day 1', Orchard Gallery (ORC-GAL), 1 Mar 2027 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2737,7 +2733,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Both show 'Booking request sent to Venue Staff.' and the request is Pending.</t>
+          <t>1. 'SPM42 Town Hall already has a venue booking request (Orchard Seminar Room, Pending).'
+2. 'Day 1 already has a venue booking request (Orchard Seminar Room, Pending).'
+No new request is created; Session 'Day 2' and 'Day 3' are unaffected.</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2846,11 +2844,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.5" customHeight="1">
+          <t>SPM-42-TC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2858,12 +2856,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>TC04 and TC09 have been run (SPM42 Town Hall and Session 'Day 1' each have a Pending request).
-Logged in as Daniel Tan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.5" customHeight="1">
+          <t>Run npm run fixtures:spm42.
+Logged in as Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123), assigned to spm42_symposium 'SPM42 Research Symposium' (status Planning, 4 Mar 2027 (2026-09-26 + 159) 09:00-18:00, expects 200, layout Theatre, no sessions).
+Changi Conference Centre (CBP-CONF) has Theatre capacity 260.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="152.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2871,15 +2870,18 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event
-2. Open the Venue tab (Find a venue), choosing the session where there is one
-3. Click 'Request booking' on the venue
-4. Click 'Submit request' with the date and slots already filled in
-5. Repeat for the next attempt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
+          <t>1. Open the event 'SPM42 Research Symposium'
+2. Open the Venue tab (Find a venue)
+3. Find 'Changi Conference Centre (CBP-CONF)' in the results
+4. Click 'Request booking' on it
+5. Tick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' for 4 Mar 2027
+6. Type the text below into 'Venue requirements'
+7. Click 'Submit request'
+8. Log out, log in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123) and click 'Booking Requests' in the sidebar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="85" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2887,12 +2889,15 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. SPM42 Town Hall, Orchard Studio (ORC-STU), 6 Mar 2027 AM + PM
-2. SPM42 Three-Session Forum, Session 'Day 1', Orchard Gallery (ORC-GAL), 1 Mar 2027 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1">
+          <t>Event: SPM42 Research Symposium
+Venue: Changi Conference Centre (CBP-CONF)
+Date: 4 Mar 2027 (2026-09-26 + 159)
+Slots: AM, PM
+Venue requirements: Lectern and stage riser at the front; two wireless microphones; doors open 08:30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2900,9 +2905,10 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>1. 'SPM42 Town Hall already has a venue booking request (Orchard Seminar Room, Pending).'
-2. 'Day 1 already has a venue booking request (Orchard Seminar Room, Pending).'
-No new request is created; Session 'Day 2' and 'Day 3' are unaffected.</t>
+          <t>Changi Conference Centre is shown as Suitable.
+The booking request screen opens for 'SPM42 Research Symposium' at 'Changi Conference Centre (CBP-CONF)'.
+After submitting, 'Booking request sent to Venue Staff.' is shown.
+Marcus Wong sees the request with Layout 'Theatre' and the requirements exactly as typed.</t>
         </is>
       </c>
     </row>
@@ -2979,119 +2985,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="75" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Question / ambiguity for the PO or developer</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44.5" customHeight="1">
-      <c r="A2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>The Jira issue was not fetched (the Atlassian connector is not authenticated). Story and AC1-AC8 were copied from Jira by hand on 2026-10-01.</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="58" customHeight="1">
-      <c r="A3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>The booking request screen is not built yet. Every label ('Request booking', 'Submit request', 'Session', 'Venue requirements'), the setup/turnaround lines and every quoted message are proposed wording. Build to these strings, or update the cases.</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n"/>
-    </row>
-    <row r="4" ht="17.5" customHeight="1">
-      <c r="A4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Is 'Venue requirements' optional? TC03 assumes it is.</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n"/>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Opening hours are not checked: a Night slot or a setup/turnaround slot can fall when the venue is closed (Orchard Seminar Room closes 22:00, Night runs to 24:00 - TC06 attempt 2). Should a request be refused or warned? Cases assume it is accepted.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
-      <c r="A6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>A single-session event that runs over more than one day cannot be covered by a one-date request (the team says such an event needs sessions). What should the coordinator see? No case written.</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Suitability is checked when the request is submitted. If the event's attendance or layout changes afterwards, nothing re-checks the Pending request. Should it be flagged like SPM-39's needsReview? No case written.</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="44.5" customHeight="1">
-      <c r="A8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Cases that submit requests use spm42_ fixture events, so npm run fixtures:spm42 resets them for a repeat pass. Never reseed the shared database for these cases.</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3124,11 +3017,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="98.5" customHeight="1">
+          <t>SPM-42-TC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3137,12 +3030,12 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Run npm run fixtures:spm42.
-Logged in as Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123), assigned to spm42_symposium 'SPM42 Research Symposium' (status Planning, 4 Mar 2027 (2026-09-26 + 159) 09:00-18:00, expects 200, layout Theatre, no sessions).
-Changi Conference Centre (CBP-CONF) has Theatre capacity 260.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="152.5" customHeight="1">
+Logged in as Daniel Tan, assigned to 'SPM42 Research Symposium' (expects 200, Theatre).
+One-North Auditorium (ONE-AUD) has Theatre capacity 180.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3152,16 +3045,11 @@
         <is>
           <t>1. Open the event 'SPM42 Research Symposium'
 2. Open the Venue tab (Find a venue)
-3. Find 'Changi Conference Centre (CBP-CONF)' in the results
-4. Click 'Request booking' on it
-5. Tick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' for 4 Mar 2027
-6. Type the text below into 'Venue requirements'
-7. Click 'Submit request'
-8. Log out, log in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123) and click 'Booking Requests' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="85" customHeight="1">
+3. Find 'One-North Auditorium (ONE-AUD)' in the results</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -3169,15 +3057,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM42 Research Symposium
-Venue: Changi Conference Centre (CBP-CONF)
-Date: 4 Mar 2027 (2026-09-26 + 159)
-Slots: AM, PM
-Venue requirements: Lectern and stage riser at the front; two wireless microphones; doors open 08:30.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98.5" customHeight="1">
+          <t>Venue: One-North Auditorium, Theatre capacity 180
+Expected attendance: 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3185,10 +3070,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Changi Conference Centre is shown as Suitable.
-The booking request screen opens for 'SPM42 Research Symposium' at 'Changi Conference Centre (CBP-CONF)'.
-After submitting, 'Booking request sent to Venue Staff.' is shown.
-Marcus Wong sees the request with Layout 'Theatre' and the requirements exactly as typed.</t>
+          <t>One-North Auditorium is shown greyed as not suitable with the reason 'Theatre capacity is 180 - your event expects 200.'
+It has no 'Request booking' button.</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3180,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC02</t>
+          <t>SPM-42-TC03</t>
         </is>
       </c>
     </row>
@@ -3310,12 +3193,11 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Run npm run fixtures:spm42.
-Logged in as Daniel Tan, assigned to 'SPM42 Research Symposium' (expects 200, Theatre).
-One-North Auditorium (ONE-AUD) has Theatre capacity 180.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+Logged in as Daniel Tan, assigned to spm42_morning_talk 'SPM42 Morning Talk' (status Planning, 5 Mar 2027 (2026-09-26 + 160) 10:00-12:00, no sessions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3323,13 +3205,16 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Research Symposium'
+          <t>1. Open the event 'SPM42 Morning Talk'
 2. Open the Venue tab (Find a venue)
-3. Find 'One-North Auditorium (ONE-AUD)' in the results</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+3. Click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)'
+4. Tick only 'AM (07:00–12:00)' for 5 Mar 2027
+5. Leave 'Venue requirements' empty
+6. Click 'Submit request'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -3337,12 +3222,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: One-North Auditorium, Theatre capacity 180
-Expected attendance: 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>Date: 5 Mar 2027 (2026-09-26 + 160)
+Slots: AM
+Venue requirements: (empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3350,8 +3236,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>One-North Auditorium is shown greyed as not suitable with the reason 'Theatre capacity is 180 - your event expects 200.'
-It has no 'Request booking' button.</t>
+          <t>'Booking request sent to Venue Staff.' is shown.
+The request shows 5 Mar 2027, AM (07:00–12:00) — the whole slot, not the event's own 10:00–12:00 — and Requirements 'None given'.</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3346,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC03</t>
+          <t>SPM-42-TC04</t>
         </is>
       </c>
     </row>
@@ -3473,11 +3359,11 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Run npm run fixtures:spm42.
-Logged in as Daniel Tan, assigned to spm42_morning_talk 'SPM42 Morning Talk' (status Planning, 5 Mar 2027 (2026-09-26 + 160) 10:00-12:00, no sessions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.5" customHeight="1">
+Logged in as Daniel Tan, assigned to spm42_town_hall 'SPM42 Town Hall' (status Planning, 6 Mar 2027 (2026-09-26 + 161) 09:00-17:00, no sessions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3485,12 +3371,11 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Morning Talk'
+          <t>1. Open the event 'SPM42 Town Hall'
 2. Open the Venue tab (Find a venue)
 3. Click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)'
-4. Tick only 'AM (07:00–12:00)' for 5 Mar 2027
-5. Leave 'Venue requirements' empty
-6. Click 'Submit request'</t>
+4. Check the date and slots already filled in
+5. Click 'Submit request'</t>
         </is>
       </c>
     </row>
@@ -3502,9 +3387,9 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Date: 5 Mar 2027 (2026-09-26 + 160)
-Slots: AM
-Venue requirements: (empty)</t>
+          <t>Event: SPM42 Town Hall (no sessions)
+Date: 6 Mar 2027 (2026-09-26 + 161)
+Slots: AM, PM</t>
         </is>
       </c>
     </row>
@@ -3516,8 +3401,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>'Booking request sent to Venue Staff.' is shown.
-The request shows 5 Mar 2027, AM (07:00–12:00) — the whole slot, not the event's own 10:00–12:00 — and Requirements 'None given'.</t>
+          <t>No Session field is shown. The date is 6 Mar 2027 with AM and PM already ticked (the event's own time).
+'Booking request sent to Venue Staff.' is shown.
+The request shows 6 Mar 2027, AM and PM, 07:00–18:00.</t>
         </is>
       </c>
     </row>
@@ -3626,11 +3512,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="58" customHeight="1">
+          <t>SPM-42-TC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3639,11 +3525,12 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Run npm run fixtures:spm42.
-Logged in as Daniel Tan, assigned to spm42_town_hall 'SPM42 Town Hall' (status Planning, 6 Mar 2027 (2026-09-26 + 161) 09:00-17:00, no sessions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
+Logged in as Daniel Tan, assigned to spm42_refusals 'SPM42 Refusal Checks' (status Planning, 7 Mar 2027 (2026-09-26 + 162) 09:00-17:00, no sessions).
+Booking request screen open for it at 'Orchard Seminar Room (ORC-SEM)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3651,11 +3538,10 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Town Hall'
-2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)'
-4. Check the date and slots already filled in
-5. Click 'Submit request'</t>
+          <t>1. Untick every slot
+2. Click 'Submit request'
+3. Tick 'AM (07:00–12:00)' and 'Night (19:00–24:00)', leave PM unticked
+4. Click 'Submit request'</t>
         </is>
       </c>
     </row>
@@ -3667,9 +3553,9 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM42 Town Hall (no sessions)
-Date: 6 Mar 2027 (2026-09-26 + 161)
-Slots: AM, PM</t>
+          <t>Date: 7 Mar 2027 (2026-09-26 + 162)
+Attempt 1: no slots
+Attempt 2: AM, Night</t>
         </is>
       </c>
     </row>
@@ -3681,9 +3567,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>No Session field is shown. The date is 6 Mar 2027 with AM and PM already ticked (the event's own time).
-'Booking request sent to Venue Staff.' is shown.
-The request shows 6 Mar 2027, AM and PM, 07:00–18:00.</t>
+          <t>Attempt 1 shows 'Choose at least one slot.'
+Attempt 2 shows 'Choose slots that are next to each other — AM and Night cannot be booked without PM.'
+No request is created for 'SPM42 Refusal Checks'.</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3678,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC05</t>
+          <t>SPM-42-TC06</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3691,12 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Run npm run fixtures:spm42.
-Logged in as Daniel Tan, assigned to spm42_refusals 'SPM42 Refusal Checks' (status Planning, 7 Mar 2027 (2026-09-26 + 162) 09:00-17:00, no sessions).
-Booking request screen open for it at 'Orchard Seminar Room (ORC-SEM)'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
+Logged in as Daniel Tan, assigned to the three events in Test data (all status Planning, no sessions).
+Orchard Seminar Room (ORC-SEM): setup 60 min, teardown 30 min. Changi Conference Centre (CBP-CONF): setup 120 min, teardown 90 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3818,14 +3704,17 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Untick every slot
-2. Click 'Submit request'
-3. Tick 'AM (07:00–12:00)' and 'Night (19:00–24:00)', leave PM unticked
-4. Click 'Submit request'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>1. Open the event
+2. Open the Venue tab (Find a venue)
+3. Click 'Request booking' on the venue
+4. Tick the slots for the date
+5. Read the setup and turnaround lines
+6. Click 'Submit request'
+7. Repeat for the next event</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="98.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -3833,13 +3722,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Date: 7 Mar 2027 (2026-09-26 + 162)
-Attempt 1: no slots
-Attempt 2: AM, Night</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>1. spm42_early_briefing 'SPM42 Early Briefing', 8 Mar 2027 (2026-09-26 + 163) 09:00-12:00, Orchard Seminar Room, AM
+2. spm42_late_show 'SPM42 Late Show', 9 Mar 2027 (2026-09-26 + 164) 19:00-22:00, Orchard Seminar Room, Night
+3. spm42_networking 'SPM42 Networking Evening', 11 Mar 2027 (2026-09-26 + 166) 17:00-22:00, expects 120, Banquet, Changi Conference Centre, PM + Night</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="139" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3847,9 +3736,10 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Attempt 1 shows 'Choose at least one slot.'
-Attempt 2 shows 'Choose slots that are next to each other — AM and Night cannot be booked without PM.'
-No request is created for 'SPM42 Refusal Checks'.</t>
+          <t>1. 'Setup: 7 Mar 2027 Night (19:00–24:00)' and 'Turnaround: 8 Mar 2027 PM (13:00–18:00)'.
+2. 'Setup: 9 Mar 2027 PM (13:00–18:00)' and 'Turnaround: 10 Mar 2027 AM (07:00–12:00)'.
+3. 'Setup: 11 Mar 2027 AM (07:00–12:00)' and 'Turnaround: 12 Mar 2027 AM (07:00–12:00)' — one slot each end for a two-slot event, and 120 minutes of setup still takes only one slot.
+Each request is sent and holds exactly its chosen slots plus those two.</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3848,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC06</t>
+          <t>SPM-42-TC07</t>
         </is>
       </c>
     </row>
@@ -3971,12 +3861,12 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Run npm run fixtures:spm42.
-Logged in as Daniel Tan, assigned to the three events in Test data (all status Planning, no sessions).
-Orchard Seminar Room (ORC-SEM): setup 60 min, teardown 30 min. Changi Conference Centre (CBP-CONF): setup 120 min, teardown 90 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.5" customHeight="1">
+Logged in as Daniel Tan, assigned to spm42_plain_pm 'SPM42 Plain Afternoon' (status Planning, 10 Mar 2027 (2026-09-26 + 165) 14:00-17:00, expects 30, Classroom, no sessions).
+Fixture venue 'SPM42 Plain Room' (SPM42-PLN) has setup 0 min and teardown 0 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3984,17 +3874,15 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event
+          <t>1. Open the event 'SPM42 Plain Afternoon'
 2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on the venue
-4. Tick the slots for the date
-5. Read the setup and turnaround lines
-6. Click 'Submit request'
-7. Repeat for the next event</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="98.5" customHeight="1">
+3. Click 'Request booking' on 'SPM42 Plain Room (SPM42-PLN)'
+4. Tick 'PM (13:00–18:00)' and 'Night (19:00–24:00)' for 10 Mar 2027
+5. Click 'Submit request'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4002,13 +3890,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. spm42_early_briefing 'SPM42 Early Briefing', 8 Mar 2027 (2026-09-26 + 163) 09:00-12:00, Orchard Seminar Room, AM
-2. spm42_late_show 'SPM42 Late Show', 9 Mar 2027 (2026-09-26 + 164) 19:00-22:00, Orchard Seminar Room, Night
-3. spm42_networking 'SPM42 Networking Evening', 11 Mar 2027 (2026-09-26 + 166) 17:00-22:00, expects 120, Banquet, Changi Conference Centre, PM + Night</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="139" customHeight="1">
+          <t>Venue: SPM42 Plain Room, setup 0 min, teardown 0 min
+Date: 10 Mar 2027 (2026-09-26 + 165)
+Slots: PM, Night (the event only needs PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4016,10 +3904,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>1. 'Setup: 7 Mar 2027 Night (19:00–24:00)' and 'Turnaround: 8 Mar 2027 PM (13:00–18:00)'.
-2. 'Setup: 9 Mar 2027 PM (13:00–18:00)' and 'Turnaround: 10 Mar 2027 AM (07:00–12:00)'.
-3. 'Setup: 11 Mar 2027 AM (07:00–12:00)' and 'Turnaround: 12 Mar 2027 AM (07:00–12:00)' — one slot each end for a two-slot event, and 120 minutes of setup still takes only one slot.
-Each request is sent and holds exactly its chosen slots plus those two.</t>
+          <t>The screen shows 'No setup or turnaround needed at this venue.'
+'Booking request sent to Venue Staff.' is shown.
+The request holds 10 Mar 2027 PM and Night — nothing before or after.</t>
         </is>
       </c>
     </row>
@@ -4128,11 +4015,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-42-TC07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="85" customHeight="1">
+          <t>SPM-42-TC08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4140,13 +4027,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
-Logged in as Daniel Tan, assigned to spm42_plain_pm 'SPM42 Plain Afternoon' (status Planning, 10 Mar 2027 (2026-09-26 + 165) 14:00-17:00, expects 30, Classroom, no sessions).
-Fixture venue 'SPM42 Plain Room' (SPM42-PLN) has setup 0 min and teardown 0 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
+          <t>Run npm run fixtures:spm42 (so Day 2 has no request yet).
+Logged in as Daniel Tan, assigned to spm42_three_sessions 'SPM42 Three-Session Forum' (Day 2: 2 Mar 2027 (2026-09-26 + 157) 14:00-17:00) and to 'SPM42 Refusal Checks' (7 Mar 2027 09:00-17:00, no sessions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="152.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4154,15 +4040,15 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Plain Afternoon'
-2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on 'SPM42 Plain Room (SPM42-PLN)'
-4. Tick 'PM (13:00–18:00)' and 'Night (19:00–24:00)' for 10 Mar 2027
-5. Click 'Submit request'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>1. Open 'SPM42 Three-Session Forum', open the Venue tab, choose Session 'Day 2' and click 'Request booking' on 'Orchard Studio (ORC-STU)'
+2. Tick only 'AM (07:00–12:00)' for 2 Mar 2027 and click 'Submit request'
+3. Change the date to 1 Mar 2027, tick only 'PM (13:00–18:00)' and click 'Submit request'
+4. Open 'SPM42 Refusal Checks', open the Venue tab and click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)'
+5. Tick only 'AM (07:00–12:00)' for 7 Mar 2027 and click 'Submit request'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4170,9 +4056,9 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: SPM42 Plain Room, setup 0 min, teardown 0 min
-Date: 10 Mar 2027 (2026-09-26 + 165)
-Slots: PM, Night (the event only needs PM)</t>
+          <t>Attempt 1: Day 2, 2 Mar 2027 AM (session runs in PM)
+Attempt 2: Day 2, 1 Mar 2027 PM (Day 1's date)
+Attempt 3: SPM42 Refusal Checks, 7 Mar 2027 AM only (event runs into PM)</t>
         </is>
       </c>
     </row>
@@ -4184,9 +4070,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The screen shows 'No setup or turnaround needed at this venue.'
-'Booking request sent to Venue Staff.' is shown.
-The request holds 10 Mar 2027 PM and Night — nothing before or after.</t>
+          <t>Attempts 1 and 2 show 'The chosen slots do not cover the session's time (2 Mar 2027, 14:00–17:00).'
+Attempt 3 shows 'The chosen slots do not cover the event's time (7 Mar 2027, 09:00–17:00).'
+No request is created.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-42_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-42_Test_Cases.xlsx
@@ -23,7 +23,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC14" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC15" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC16" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC17" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -463,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -919,7 +918,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>A booking can only be requested once the event is Approved or in Planning (team decision)</t>
+          <t>A venue cannot be requested for a completed, cancelled or rejected event (existing SPM-47 rule)</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1034,94 +1033,62 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>TC17</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>SPM-42-TC17</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>An event or session with an active request cannot request a second venue (#109)</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>AC4, AC5</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Covered by</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="44.5" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>AC1</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>The Event Coordinator can select a suitable venue.</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="9" t="n"/>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Covered by</t>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>SPM-42-TC01
+SPM-42-TC02
+SPM-42-TC12</t>
         </is>
       </c>
       <c r="F23" s="9" t="n"/>
     </row>
-    <row r="24" ht="44.5" customHeight="1">
+    <row r="24" ht="125.5" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>AC1</t>
+          <t>AC2</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>The Event Coordinator can select a suitable venue.</t>
+          <t>The request specifies one or more of the venue's fixed AM, PM or Night slots for the required date; an event spanning multiple slots consumes each of them in full.</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>SPM-42-TC01
-SPM-42-TC02
-SPM-42-TC12</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="125.5" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>AC2</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>The request specifies one or more of the venue's fixed AM, PM or Night slots for the required date; an event spanning multiple slots consumes each of them in full.</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>SPM-42-TC03
 SPM-42-TC04
@@ -1134,22 +1101,22 @@
 SPM-42-TC16</t>
         </is>
       </c>
-      <c r="F25" s="9" t="n"/>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Where setup or turnaround time is required, the immediately adjacent slot (before the event for setup, after for turnaround, including the previous or following day where applicable) is included in the request.</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>SPM-42-TC06
 SPM-42-TC07
@@ -1157,123 +1124,121 @@
 SPM-42-TC16</t>
         </is>
       </c>
+      <c r="F25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="44.5" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>AC4</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>For a multi-session event, a booking request is made per session, using that session's own date, time and requirements rather than the event's.</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>SPM-42-TC04
+SPM-42-TC08
+SPM-42-TC09</t>
+        </is>
+      </c>
       <c r="F26" s="9" t="n"/>
     </row>
-    <row r="27" ht="58" customHeight="1">
+    <row r="27" ht="31" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>AC4</t>
+          <t>AC5</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>For a multi-session event, a booking request is made per session, using that session's own date, time and requirements rather than the event's.</t>
+          <t>The request is associated with the relevant event (and session, where applicable).</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>SPM-42-TC04
-SPM-42-TC08
-SPM-42-TC09
-SPM-42-TC17</t>
+          <t>SPM-42-TC09
+SPM-42-TC10</t>
         </is>
       </c>
       <c r="F27" s="9" t="n"/>
     </row>
-    <row r="28" ht="44.5" customHeight="1">
+    <row r="28" ht="31" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>AC5</t>
+          <t>AC6</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>The request is associated with the relevant event (and session, where applicable).</t>
+          <t>Venue requirements are included in the request.</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>SPM-42-TC09
-SPM-42-TC10
-SPM-42-TC17</t>
+          <t>SPM-42-TC01
+SPM-42-TC03</t>
         </is>
       </c>
       <c r="F28" s="9" t="n"/>
     </row>
-    <row r="29" ht="31" customHeight="1">
+    <row r="29" ht="44.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>AC6</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Venue requirements are included in the request.</t>
+          <t>The request is submitted to Venue Staff for review.</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>SPM-42-TC01
-SPM-42-TC03</t>
+          <t>SPM-42-TC11
+SPM-42-TC12
+SPM-42-TC13</t>
         </is>
       </c>
       <c r="F29" s="9" t="n"/>
     </row>
-    <row r="30" ht="44.5" customHeight="1">
+    <row r="30" ht="17.5" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>AC7</t>
+          <t>AC8</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>The request is submitted to Venue Staff for review.</t>
+          <t>The venue booking request has a pending status.</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>SPM-42-TC11
-SPM-42-TC12
-SPM-42-TC13</t>
+          <t>SPM-42-TC11</t>
         </is>
       </c>
       <c r="F30" s="9" t="n"/>
     </row>
-    <row r="31" ht="17.5" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>AC8</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>The venue booking request has a pending status.</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>SPM-42-TC11</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="n"/>
-    </row>
-    <row r="33" ht="166" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="32" ht="166" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>src/lib/venueBookingRequest.ts
 src/lib/__tests__/venueBookingRequest.test.ts
@@ -1289,10 +1254,10 @@
 docs/CUSTOMER_CLARIFICATIONS.md</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="9" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1305,17 +1270,17 @@
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="E31:F31"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B31:D31"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1334,7 +1299,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1373,7 +1337,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="125.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1381,12 +1345,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
-Logged in as Daniel Tan, assigned to spm42_three_sessions 'SPM42 Three-Session Forum' (status Approved; opening the Venue tab moves it to Planning, SPM-40). Sessions: 'Day 1' 1 Mar 2027 (2026-09-26 + 156) 09:00-12:00, expects 80, Theatre; 'Day 2' 2 Mar 2027 (2026-09-26 + 157) 14:00-17:00, expects 30, Classroom; 'Day 3' 3 Mar 2027 (2026-09-26 + 158) 19:00-22:00, expects 60, Banquet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="166" customHeight="1">
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
+Logged in as Daniel Tan, assigned to spm42_three_sessions 'SPM42 Three-Session Forum' (status Approved). Sessions: 'Day 1' 1 Mar 2027 (2026-09-26 + 156) 09:00-12:00, expects 80, Theatre; 'Day 2' 2 Mar 2027 (2026-09-26 + 157) 14:00-17:00, expects 30, Classroom; 'Day 3' 3 Mar 2027 (2026-09-26 + 158) 19:00-22:00, expects 60, Banquet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="287.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1394,12 +1358,20 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Three-Session Forum'
-2. Open the Venue tab (Find a venue)
-3. Choose Session 'Day 1', click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)', check the date and slot shown, click 'Submit request'
-4. Choose Session 'Day 2', click 'Request booking' on 'Orchard Studio (ORC-STU)', check the date and slot shown, click 'Submit request'
-5. Choose Session 'Day 3', click 'Request booking' on 'Orchard Gallery (ORC-GAL)', check the date and slot shown, click 'Submit request'
-6. Look at the event's booking requests</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Three-Session Forum' in the list
+4. Click the 'Venue' tab
+5. In the 'Session' drop-down, choose 'Day 1'
+6. Find 'Orchard Seminar Room (ORC-SEM)' in the venue list and click its 'Request booking' button
+7. Check the Session, Date, ticked slot and Layout shown, then click 'Submit request' and click 'Back to Venue'
+8. In the 'Session' drop-down, choose 'Day 2'
+9. Find 'Orchard Studio (ORC-STU)' in the venue list and click its 'Request booking' button
+10. Check the Session, Date, ticked slot and Layout shown, then click 'Submit request' and click 'Back to Venue'
+11. In the 'Session' drop-down, choose 'Day 3'
+12. Find 'Orchard Gallery (ORC-GAL)' in the venue list and click its 'Request booking' button
+13. Check the Session, Date, ticked slot and Layout shown, then click 'Submit request' and click 'Back to Venue'
+14. Read the three requests under 'Booking requests'</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1524,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1">
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1560,10 +1532,11 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Booking Requests' in the sidebar
-2. Find the request for Orchard Seminar Room on 6 Mar 2027
-3. Find the request for Orchard Studio on 2 Mar 2027
-4. Click the event reference on one of them</t>
+          <t>1. Log in as marcus.wong@connectsphere.com / password123
+2. Click 'Booking Requests' in the sidebar
+3. Find the row for Orchard Seminar Room on 6 Mar 2027 and read its Event column
+4. Find the row for Orchard Studio on 2 Mar 2027 and read its Event column
+5. Click the EVT- reference in the 2 Mar row</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1687,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1">
+    <row r="4" ht="152.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1722,8 +1695,14 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. As Daniel Tan, open 'SPM42 Town Hall', open the Venue tab and look at its booking requests
-2. Log in as Venue Staff Marcus Wong and click 'Booking Requests' in the sidebar</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Town Hall' in the list
+4. Click the 'Venue' tab
+5. Read the status badge of the request under 'Booking requests'
+6. Log out, then log in as marcus.wong@connectsphere.com / password123
+7. Click 'Booking Requests' in the sidebar
+8. Find the row for SPM42 Town Hall and read every column</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1718,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="71.5" customHeight="1">
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1748,7 +1727,7 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Both screens show the request with the status badge 'Pending'.
-Marcus Wong's list shows venue Orchard Seminar Room, 6 Mar 2027, AM and PM, setup 5 Mar 2027 Night, turnaround 6 Mar 2027 Night, requested by Daniel Tan.</t>
+Marcus Wong's row shows Orchard Seminar Room, '6 Mar 2027 · AM, PM (07:00–18:00)', 'Setup: 5 Mar 2027 Night (19:00–24:00)', 'Turnaround: 6 Mar 2027 Night (19:00–24:00)', and Requested by Daniel Tan.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1853,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="44.5" customHeight="1">
+    <row r="4" ht="260.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1882,9 +1861,15 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Log in as each account in turn
-2. Open the event 'Town Hall Q4'
-3. Open the Venue tab if it is shown</t>
+          <t>1. Log in as priya.raj@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'Town Hall Q4' in the list
+4. Click the 'Venue' tab
+5. Read the message above the venue list and look for any 'Request booking' button
+6. Log out, log in as rachel.ng@meridianfina.com / password123, click 'My Events', click 'Town Hall Q4' and look for a 'Venue' tab
+7. Log out, log in as grace.lim@connectsphere.com / password123, click 'All Events', click 'Town Hall Q4' and look for a 'Venue' tab
+8. Log out, log in as marcus.wong@connectsphere.com / password123, click 'Booking Requests' and look for any 'Request booking' button
+9. Log out, log in as kenji.sato@connectsphere.com / password123 and look through the sidebar for anywhere to request a venue</t>
         </is>
       </c>
     </row>
@@ -2031,11 +2016,11 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Seeded data.
-Logged in as Coordinator Priya Raj (priya.raj@connectsphere.com / password123), assigned to 'Kirana Regional Managers Offsite' (status Under review, 22 Nov 2026 (2026-09-26 + 57) 09:00-17:00).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31" customHeight="1">
+Logged in as Coordinator Joel Fernandez (joel.fernandez@connectsphere.com / password123), assigned to 'Pearl Delta Supplier Forum' (status Cancelled, 29 Oct 2026 (2026-09-26 + 33) 09:00-14:00).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2043,8 +2028,11 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'Kirana Regional Managers Offsite'
-2. Open the Venue tab (Find a venue)</t>
+          <t>1. Log in as joel.fernandez@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'Pearl Delta Supplier Forum' in the list
+4. Click the 'Venue' tab
+5. Read the message above the venue list and look for any 'Request booking' button</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2044,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event status: Under review</t>
+          <t>Event status: Cancelled</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2057,7 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>No 'Request booking' button is shown.
-The page says 'A venue booking can only be requested once the event is Approved or in Planning.'</t>
+The page says 'A venue cannot be requested for a completed, cancelled or rejected event.'</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2170,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="139" customHeight="1">
+    <row r="3" ht="166" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2190,7 +2178,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42. Seeded data, unchanged:
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones). Seeded data, unchanged:
 - 'Product Showcase' has an Approved booking at Marina Auditorium (MAR-AUD), 21 Oct 2026 (2026-09-26 + 25) 11:00-15:00.
 - 'Pearl Delta Safety Conference' has a Pending booking at Changi Conference Centre (CBP-CONF), 14 Dec 2026 (2026-09-26 + 79) 09:00-17:00.
 - Marina Auditorium is unavailable for maintenance 20-21 Nov 2026 (2026-09-26 + 55 to + 56).
@@ -2198,7 +2186,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="98.5" customHeight="1">
+    <row r="4" ht="382" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2206,12 +2194,22 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event
-2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on the venue
-4. Tick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' for the date
-5. Click 'Submit request'
-6. Repeat for the next event</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Clash Check' in the list
+4. Click the 'Venue' tab
+5. Find 'Marina Auditorium (MAR-AUD)' in the venue list and click its 'Request booking' button
+6. Make sure 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked for 21 Oct 2026, click 'Submit request' and read the message
+7. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+8. Click 'Staff Retreat' in the list
+9. Click the 'Venue' tab
+10. Find 'Changi Conference Centre (CBP-CONF)' in the venue list and click its 'Request booking' button
+11. Make sure 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked for 14 Dec 2026, click 'Submit request' and read the message
+12. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+13. Click 'Sports Meet' in the list
+14. Click the 'Venue' tab
+15. Find 'Marina Auditorium (MAR-AUD)' in the venue list and click its 'Request booking' button
+16. Make sure 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked for 20 Nov 2026, click 'Submit request' and read the message</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2364,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="71.5" customHeight="1">
+    <row r="4" ht="139" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2374,11 +2372,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'Keynote Rehearsal'
-2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on 'Marina Auditorium (MAR-AUD)'
-4. Tick only 'PM (13:00–18:00)' for 20 Oct 2026
-5. Click 'Submit request'</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'Keynote Rehearsal' in the list
+4. Click the 'Venue' tab
+5. Find 'Marina Auditorium (MAR-AUD)' in the venue list and click its 'Request booking' button
+6. Make sure only 'PM (13:00–18:00)' is ticked for 20 Oct 2026
+7. Click 'Submit request' and read the message</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="139" customHeight="1">
+    <row r="3" ht="166" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2525,14 +2525,14 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42. It creates:
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones). It creates:
 - 'SPM42 Cancelled Hold' with a Cancelled booking at Orchard Gallery (ORC-GAL), 15 Mar 2027 (2026-09-26 + 170) 09:00-17:00.
 - 'SPM42 Rejected Hold' with a Rejected booking at Marina Auditorium (MAR-AUD), 16 Mar 2027 (2026-09-26 + 171) 09:00-18:00 — had it been approved, its turnaround would hold 16 Mar Night.
 Logged in as Daniel Tan, assigned to the two events in Test data (status Planning, no sessions).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="98.5" customHeight="1">
+    <row r="4" ht="314.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2540,12 +2540,19 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event
-2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on the venue
-4. Tick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' for the date
-5. Click 'Submit request'
-6. Repeat for the next event</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 After Cancellation' in the list
+4. Click the 'Venue' tab
+5. Find 'Orchard Gallery (ORC-GAL)' in the venue list and click its 'Request booking' button
+6. Make sure 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked for 15 Mar 2027, click 'Submit request' and read the message
+7. Click 'Back to Venue' and read the status under 'Booking requests'
+8. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+9. Click 'SPM42 After Rejection' in the list
+10. Click the 'Venue' tab
+11. Find 'Marina Auditorium (MAR-AUD)' in the venue list and click its 'Request booking' button
+12. Make sure 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked for 17 Mar 2027, click 'Submit request' and read the message
+13. Click 'Back to Venue' and read the status under 'Booking requests'</t>
         </is>
       </c>
     </row>
@@ -2571,171 +2578,6 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Both show 'Booking request sent to Venue Staff.' and the request is Pending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>46296</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-42-TC17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.5" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>TC04 and TC09 have been run (SPM42 Town Hall and Session 'Day 1' each have a Pending request).
-Logged in as Daniel Tan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the event
-2. Open the Venue tab (Find a venue), choosing the session where there is one
-3. Click 'Request booking' on the venue
-4. Click 'Submit request' with the date and slots already filled in
-5. Repeat for the next attempt</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>1. SPM42 Town Hall, Orchard Studio (ORC-STU), 6 Mar 2027 AM + PM
-2. SPM42 Three-Session Forum, Session 'Day 1', Orchard Gallery (ORC-GAL), 1 Mar 2027 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>1. 'SPM42 Town Hall already has a venue booking request (Orchard Seminar Room, Pending).'
-2. 'Day 1 already has a venue booking request (Orchard Seminar Room, Pending).'
-No new request is created; Session 'Day 2' and 'Day 3' are unaffected.</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2690,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="98.5" customHeight="1">
+    <row r="3" ht="125.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2856,13 +2698,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123), assigned to spm42_symposium 'SPM42 Research Symposium' (status Planning, 4 Mar 2027 (2026-09-26 + 159) 09:00-18:00, expects 200, layout Theatre, no sessions).
 Changi Conference Centre (CBP-CONF) has Theatre capacity 260.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="152.5" customHeight="1">
+    <row r="4" ht="260.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2870,14 +2712,18 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Research Symposium'
-2. Open the Venue tab (Find a venue)
-3. Find 'Changi Conference Centre (CBP-CONF)' in the results
-4. Click 'Request booking' on it
-5. Tick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' for 4 Mar 2027
-6. Type the text below into 'Venue requirements'
-7. Click 'Submit request'
-8. Log out, log in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123) and click 'Booking Requests' in the sidebar</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Research Symposium' in the list
+4. Click the 'Venue' tab
+5. Find 'Changi Conference Centre (CBP-CONF)' in the venue list and check the badge next to it
+6. Click 'Request booking' on Changi Conference Centre
+7. Check the Date shows 4 Mar 2027 and only 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked
+8. Click in the 'Venue requirements' box and type: Lectern and stage riser at the front; two wireless microphones; doors open 08:30.
+9. Click 'Submit request'
+10. Log out, then log in as marcus.wong@connectsphere.com / password123
+11. Click 'Booking Requests' in the sidebar
+12. Find the row for SPM42 Research Symposium and read its Layout and Requirements</t>
         </is>
       </c>
     </row>
@@ -3021,7 +2867,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3029,13 +2875,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Daniel Tan, assigned to 'SPM42 Research Symposium' (expects 200, Theatre).
 One-North Auditorium (ONE-AUD) has Theatre capacity 180.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44.5" customHeight="1">
+    <row r="4" ht="112" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3043,9 +2889,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Research Symposium'
-2. Open the Venue tab (Find a venue)
-3. Find 'One-North Auditorium (ONE-AUD)' in the results</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Research Symposium' in the list
+4. Click the 'Venue' tab
+5. Find 'One-North Auditorium (ONE-AUD)' in the venue list
+6. Read the badge and the reason shown under it
+7. Look for a 'Request booking' button on it</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3034,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3192,12 +3042,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Daniel Tan, assigned to spm42_morning_talk 'SPM42 Morning Talk' (status Planning, 5 Mar 2027 (2026-09-26 + 160) 10:00-12:00, no sessions).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="98.5" customHeight="1">
+    <row r="4" ht="247" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3205,12 +3055,18 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Morning Talk'
-2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)'
-4. Tick only 'AM (07:00–12:00)' for 5 Mar 2027
-5. Leave 'Venue requirements' empty
-6. Click 'Submit request'</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Morning Talk' in the list
+4. Click the 'Venue' tab
+5. Find 'Orchard Seminar Room (ORC-SEM)' in the venue list and click its 'Request booking' button
+6. Check the Date shows 5 Mar 2027 and only 'AM (07:00–12:00)' is ticked
+7. Leave the 'Venue requirements' box empty
+8. Click 'Submit request'
+9. Click 'Back to Venue' and read the request under 'Booking requests'
+10. Log out, then log in as marcus.wong@connectsphere.com / password123
+11. Click 'Booking Requests' in the sidebar
+12. Find the row for SPM42 Morning Talk and read its Requirements</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3237,7 +3093,8 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>'Booking request sent to Venue Staff.' is shown.
-The request shows 5 Mar 2027, AM (07:00–12:00) — the whole slot, not the event's own 10:00–12:00 — and Requirements 'None given'.</t>
+Under 'Booking requests' the request reads '5 Mar 2027 · AM (07:00–12:00)' — the whole slot, not the event's own 10:00–12:00.
+Marcus Wong's Booking Requests row shows Requirements 'None given'.</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3207,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3358,12 +3215,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Daniel Tan, assigned to spm42_town_hall 'SPM42 Town Hall' (status Planning, 6 Mar 2027 (2026-09-26 + 161) 09:00-17:00, no sessions).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="85" customHeight="1">
+    <row r="4" ht="193" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3371,11 +3228,15 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Town Hall'
-2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)'
-4. Check the date and slots already filled in
-5. Click 'Submit request'</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Town Hall' in the list
+4. Click the 'Venue' tab
+5. Check there is no 'Session' drop-down above the venue list
+6. Find 'Orchard Seminar Room (ORC-SEM)' in the venue list and click its 'Request booking' button
+7. Check the Date shows 6 Mar 2027 and 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are already ticked
+8. Click 'Submit request'
+9. Click 'Back to Venue' and read the request under 'Booking requests'</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3254,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3401,9 +3262,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>No Session field is shown. The date is 6 Mar 2027 with AM and PM already ticked (the event's own time).
+          <t>No Session drop-down is shown. The Date is 6 Mar 2027 with AM and PM already ticked (the event's own time).
 'Booking request sent to Venue Staff.' is shown.
-The request shows 6 Mar 2027, AM and PM, 07:00–18:00.</t>
+Under 'Booking requests' the request reads '6 Mar 2027 · AM, PM (07:00–18:00)'.</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3377,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3524,13 +3385,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Daniel Tan, assigned to spm42_refusals 'SPM42 Refusal Checks' (status Planning, 7 Mar 2027 (2026-09-26 + 162) 09:00-17:00, no sessions).
 Booking request screen open for it at 'Orchard Seminar Room (ORC-SEM)'.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="71.5" customHeight="1">
+    <row r="4" ht="206.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3538,10 +3399,16 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Untick every slot
-2. Click 'Submit request'
-3. Tick 'AM (07:00–12:00)' and 'Night (19:00–24:00)', leave PM unticked
-4. Click 'Submit request'</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Refusal Checks' in the list
+4. Click the 'Venue' tab
+5. Find 'Orchard Seminar Room (ORC-SEM)' in the venue list and click its 'Request booking' button
+6. Untick 'AM (07:00–12:00)' and 'PM (13:00–18:00)' so no slot is ticked
+7. Click 'Submit request' and read the message
+8. Tick 'AM (07:00–12:00)' and 'Night (19:00–24:00)'; leave 'PM (13:00–18:00)' unticked
+9. Click 'Submit request' and read the message
+10. Click 'Cancel' and check 'Booking requests' on the Venue tab</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3549,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3690,13 +3557,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Daniel Tan, assigned to the three events in Test data (all status Planning, no sessions).
 Orchard Seminar Room (ORC-SEM): setup 60 min, teardown 30 min. Changi Conference Centre (CBP-CONF): setup 120 min, teardown 90 min.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="98.5" customHeight="1">
+    <row r="4" ht="382" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3704,13 +3571,22 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event
-2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on the venue
-4. Tick the slots for the date
-5. Read the setup and turnaround lines
-6. Click 'Submit request'
-7. Repeat for the next event</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Early Briefing' in the list
+4. Click the 'Venue' tab
+5. Find 'Orchard Seminar Room (ORC-SEM)' in the venue list and click its 'Request booking' button
+6. Check only 'AM (07:00–12:00)' is ticked for 8 Mar 2027, read the 'Setup:' and 'Turnaround:' lines, then click 'Submit request'
+7. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+8. Click 'SPM42 Late Show' in the list
+9. Click the 'Venue' tab
+10. Find 'Orchard Seminar Room (ORC-SEM)' in the venue list and click its 'Request booking' button
+11. Check only 'Night (19:00–24:00)' is ticked for 9 Mar 2027, read the 'Setup:' and 'Turnaround:' lines, then click 'Submit request'
+12. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+13. Click 'SPM42 Networking Evening' in the list
+14. Click the 'Venue' tab
+15. Find 'Changi Conference Centre (CBP-CONF)' in the venue list and click its 'Request booking' button
+16. Check only 'PM (13:00–18:00)' and 'Night (19:00–24:00)' are ticked for 11 Mar 2027, read the 'Setup:' and 'Turnaround:' lines, then click 'Submit request'</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3728,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3860,13 +3736,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42.
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Daniel Tan, assigned to spm42_plain_pm 'SPM42 Plain Afternoon' (status Planning, 10 Mar 2027 (2026-09-26 + 165) 14:00-17:00, expects 30, Classroom, no sessions).
 Fixture venue 'SPM42 Plain Room' (SPM42-PLN) has setup 0 min and teardown 0 min.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="85" customHeight="1">
+    <row r="4" ht="193" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3874,11 +3750,16 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the event 'SPM42 Plain Afternoon'
-2. Open the Venue tab (Find a venue)
-3. Click 'Request booking' on 'SPM42 Plain Room (SPM42-PLN)'
-4. Tick 'PM (13:00–18:00)' and 'Night (19:00–24:00)' for 10 Mar 2027
-5. Click 'Submit request'</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Plain Afternoon' in the list
+4. Click the 'Venue' tab
+5. Find 'SPM42 Plain Room (SPM42-PLN)' in the venue list and click its 'Request booking' button
+6. Read the line under the slots
+7. Tick 'Night (19:00–24:00)' as well, so 'PM (13:00–18:00)' and 'Night (19:00–24:00)' are both ticked for 10 Mar 2027
+8. Check the line under the slots has not changed
+9. Click 'Submit request'
+10. Click 'Back to Venue' and read the request under 'Booking requests'</t>
         </is>
       </c>
     </row>
@@ -3904,9 +3785,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The screen shows 'No setup or turnaround needed at this venue.'
+          <t>Before and after ticking Night, the line under the slots reads 'No setup or turnaround needed at this venue.'
 'Booking request sent to Venue Staff.' is shown.
-The request holds 10 Mar 2027 PM and Night — nothing before or after.</t>
+Under 'Booking requests' the request reads '10 Mar 2027 · PM, Night (13:00–24:00)' — nothing before or after.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +3900,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4027,12 +3908,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Run npm run fixtures:spm42 (so Day 2 has no request yet).
+          <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones). Run this case before TC09, so Day 2 has no request yet.
 Logged in as Daniel Tan, assigned to spm42_three_sessions 'SPM42 Three-Session Forum' (Day 2: 2 Mar 2027 (2026-09-26 + 157) 14:00-17:00) and to 'SPM42 Refusal Checks' (7 Mar 2027 09:00-17:00, no sessions).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="152.5" customHeight="1">
+    <row r="4" ht="287.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4040,11 +3921,19 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open 'SPM42 Three-Session Forum', open the Venue tab, choose Session 'Day 2' and click 'Request booking' on 'Orchard Studio (ORC-STU)'
-2. Tick only 'AM (07:00–12:00)' for 2 Mar 2027 and click 'Submit request'
-3. Change the date to 1 Mar 2027, tick only 'PM (13:00–18:00)' and click 'Submit request'
-4. Open 'SPM42 Refusal Checks', open the Venue tab and click 'Request booking' on 'Orchard Seminar Room (ORC-SEM)'
-5. Tick only 'AM (07:00–12:00)' for 7 Mar 2027 and click 'Submit request'</t>
+          <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 Three-Session Forum' in the list
+4. Click the 'Venue' tab
+5. In the 'Session' drop-down, choose 'Day 2'
+6. Find 'Orchard Studio (ORC-STU)' in the venue list and click its 'Request booking' button
+7. Untick 'PM (13:00–18:00)', tick only 'AM (07:00–12:00)', then click 'Submit request' and read the message
+8. Change the Date to 1 Mar 2027, tick only 'PM (13:00–18:00)', then click 'Submit request' and read the message
+9. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+10. Click 'SPM42 Refusal Checks' in the list
+11. Click the 'Venue' tab
+12. Find 'Orchard Seminar Room (ORC-SEM)' in the venue list and click its 'Request booking' button
+13. Untick 'PM (13:00–18:00)' so only 'AM (07:00–12:00)' is ticked for 7 Mar 2027, then click 'Submit request' and read the message</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-42_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-42_Test_Cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samis\OneDrive\Documents\Is212spm\IS212-1\docs\test-cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IS212\docs\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821BB33E-A85B-4B26-91D4-AEC2277F2FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD8AB7E-6775-4CAE-9F25-77AD6737301A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="14" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,95 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="203">
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>SPM-42-TC16</t>
+  </si>
+  <si>
+    <t>Pre-conditions</t>
+  </si>
+  <si>
+    <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones). It creates:
+- 'SPM42 Cancelled Hold' with a Cancelled booking at Orchard Gallery (ORC-GAL), 15 Mar 2027 (2026-09-26 + 170) 09:00-17:00.
+- 'SPM42 Rejected Hold' with a Rejected booking at Marina Auditorium (MAR-AUD), 16 Mar 2027 (2026-09-26 + 171) 09:00-18:00 — had it been approved, its turnaround would hold 16 Mar Night.
+Logged in as Daniel Tan, assigned to the two events in Test data (status Planning, no sessions).</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>1. Log in as daniel.tan@connectsphere.com / password123
+2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+3. Click 'SPM42 After Cancellation' in the list
+4. Click the 'Venue' tab
+5. Find 'Orchard Gallery (ORC-GAL)' in the venue list and click its 'Request booking' button
+6. Make sure 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked for 15 Mar 2027, click 'Submit request' and read the message
+7. Click 'Back to Venue' and read the status under 'Booking requests'
+8. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
+9. Click 'SPM42 After Rejection' in the list
+10. Click the 'Venue' tab
+11. Find 'Marina Auditorium (MAR-AUD)' in the venue list and click its 'Request booking' button
+12. Make sure 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked for 17 Mar 2027, click 'Submit request' and read the message
+13. Click 'Back to Venue' and read the status under 'Booking requests'</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>1. spm42_after_cancel 'SPM42 After Cancellation', 15 Mar 2027 10:00-16:00, Orchard Gallery (same slots as the cancelled booking)
+2. spm42_after_reject 'SPM42 After Rejection', 17 Mar 2027 (2026-09-26 + 172) 10:00-16:00, Marina Auditorium (its setup takes 16 Mar Night)</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Both show 'Booking request sent to Venue Staff.' and the request is Pending.</t>
+  </si>
+  <si>
+    <t>Created By</t>
+  </si>
+  <si>
+    <t>Sammi Chua</t>
+  </si>
+  <si>
+    <t>Creation Date</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Pass/Fail/Not Executed/Blocked</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Executed by</t>
+  </si>
+  <si>
+    <t>Sammi</t>
+  </si>
+  <si>
+    <t>Date of Execution</t>
+  </si>
+  <si>
+    <t>SPM42 After Cancellation at Orchard Gallery, over the same slots as the cancelled booking: 'Booking request sent to Venue Staff.', status Pending. SPM42 After Rejection at Marina Auditorium, whose setup needs the slot a rejected booking's turnaround would have held: also sent and Pending.</t>
+  </si>
+  <si>
+    <t>Neither a cancelled nor a rejected booking holds a slot (#41), including the setup and turnaround slots either side of it.</t>
+  </si>
   <si>
     <t>Story</t>
   </si>
@@ -47,9 +135,6 @@
     <t>Sheet</t>
   </si>
   <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -252,9 +337,6 @@
   </si>
   <si>
     <t>TC16</t>
-  </si>
-  <si>
-    <t>SPM-42-TC16</t>
   </si>
   <si>
     <t>Cancelled and rejected bookings do not block a request (#41)</t>
@@ -362,18 +444,9 @@
 docs/CUSTOMER_CLARIFICATIONS.md</t>
   </si>
   <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Pre-conditions</t>
-  </si>
-  <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123), assigned to spm42_symposium 'SPM42 Research Symposium' (status Planning, 4 Mar 2027 (2026-09-26 + 159) 09:00-18:00, expects 200, layout Theatre, no sessions).
 Changi Conference Centre (CBP-CONF) has Theatre capacity 260.</t>
-  </si>
-  <si>
-    <t>Test Steps</t>
   </si>
   <si>
     <t>1. Log in as daniel.tan@connectsphere.com / password123
@@ -390,9 +463,6 @@
 12. Find the row for SPM42 Research Symposium and read its Layout and Requirements</t>
   </si>
   <si>
-    <t>Test Data</t>
-  </si>
-  <si>
     <t>Event: SPM42 Research Symposium
 Venue: Changi Conference Centre (CBP-CONF)
 Date: 4 Mar 2027 (2026-09-26 + 159)
@@ -400,37 +470,13 @@
 Venue requirements: Lectern and stage riser at the front; two wireless microphones; doors open 08:30.</t>
   </si>
   <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
     <t>Changi Conference Centre is shown as Suitable.
 The booking request screen opens for 'SPM42 Research Symposium' at 'Changi Conference Centre (CBP-CONF)'.
 After submitting, 'Booking request sent to Venue Staff.' is shown.
 Marcus Wong sees the request with Layout 'Theatre' and the requirements exactly as typed.</t>
   </si>
   <si>
-    <t>Created By</t>
-  </si>
-  <si>
-    <t>Sammi Chua</t>
-  </si>
-  <si>
-    <t>Creation Date</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Pass/Fail/Not Executed/Blocked</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Executed by</t>
-  </si>
-  <si>
-    <t>Date of Execution</t>
+    <t>Changi Conference Centre showed the status chip 'Suitable' with no blocking reasons and a Request booking button. The booking screen opened for the event at that venue; after entering 'Theatre layout, lectern and roving mic.' and submitting, 'Booking request sent to Venue Staff.' was shown. On Marcus Wong's Booking Requests screen the row reads: 'SPM42 Research Symposium | Changi Conference Centre (CBP-CONF) | 4 Mar 2027 · AM, PM (07:00-18:00) | Layout: Theatre | Theatre layout, lectern and roving mic. | Daniel Tan | Pending'.</t>
   </si>
   <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
@@ -453,6 +499,9 @@
   <si>
     <t>One-North Auditorium is shown greyed as not suitable with the reason 'Theatre capacity is 180 - your event expects 200.'
 It has no 'Request booking' button.</t>
+  </si>
+  <si>
+    <t>One-North Auditorium showed the chip 'Not suitable' with the single reason 'Theatre capacity is 180 - your event expects 200.' Its card carried no Request booking button at all.</t>
   </si>
   <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
@@ -483,6 +532,9 @@
 Marcus Wong's Booking Requests row shows Requirements 'None given'.</t>
   </si>
   <si>
+    <t>AM was already ticked when the booking screen opened. After submitting, the request listed on the Venue tab reads '5 Mar 2027 · AM (07:00-12:00) · Theatre' with status Pending - the whole slot, not the event's own 10:00-12:00. Venue Staff's row shows the requirements as 'None given'.</t>
+  </si>
+  <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Daniel Tan, assigned to spm42_town_hall 'SPM42 Town Hall' (status Planning, 6 Mar 2027 (2026-09-26 + 161) 09:00-17:00, no sessions).</t>
   </si>
@@ -506,6 +558,9 @@
     <t>No Session drop-down is shown. The Date is 6 Mar 2027 with AM and PM already ticked (the event's own time).
 'Booking request sent to Venue Staff.' is shown.
 Under 'Booking requests' the request reads '6 Mar 2027 · AM, PM (07:00–18:00)'.</t>
+  </si>
+  <si>
+    <t>No Session drop-down was present. The booking screen opened on the event's own date with AM and PM ticked and Night clear. The request reads '6 Mar 2027 · AM, PM (07:00-18:00) · Theatre', Pending.</t>
   </si>
   <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
@@ -533,6 +588,9 @@
     <t>Attempt 1 shows 'Choose at least one slot.'
 Attempt 2 shows 'Choose slots that are next to each other — AM and Night cannot be booked without PM.'
 No request is created for 'SPM42 Refusal Checks'.</t>
+  </si>
+  <si>
+    <t>Submitting with no slot ticked showed 'Choose at least one slot.' Submitting with AM and Night ticked showed 'Choose slots that are next to each other - AM and Night cannot be booked without PM.' No request was created for the event.</t>
   </si>
   <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
@@ -569,6 +627,12 @@
 Each request is sent and holds exactly its chosen slots plus those two.</t>
   </si>
   <si>
+    <t>1. SPM42 Early Briefing at Orchard Seminar Room: 'Setup: 7 Mar 2027 Night (19:00-24:00)' and 'Turnaround: 8 Mar 2027 PM (13:00-18:00)'. 2. SPM42 Late Show: 'Setup: 9 Mar 2027 PM (13:00-18:00)' and 'Turnaround: 10 Mar 2027 AM (07:00-12:00)'. 3. SPM42 Networking Evening at Changi Conference Centre: 'Setup: 11 Mar 2027 AM (07:00-12:00)' and 'Turnaround: 12 Mar 2027 AM (07:00-12:00)'. All three requests were sent.</t>
+  </si>
+  <si>
+    <t>Confirms both day-crossing directions: an AM event's setup takes the previous day's Night, and a Night event's turnaround takes the next day's AM (#123). Case 3 also confirms 120 minutes of setup still takes exactly one slot.</t>
+  </si>
+  <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
 Logged in as Daniel Tan, assigned to spm42_plain_pm 'SPM42 Plain Afternoon' (status Planning, 10 Mar 2027 (2026-09-26 + 165) 14:00-17:00, expects 30, Classroom, no sessions).
 Fixture venue 'SPM42 Plain Room' (SPM42-PLN) has setup 0 min and teardown 0 min.</t>
@@ -594,6 +658,9 @@
     <t>Before and after ticking Night, the line under the slots reads 'No setup or turnaround needed at this venue.'
 'Booking request sent to Venue Staff.' is shown.
 Under 'Booking requests' the request reads '10 Mar 2027 · PM, Night (13:00–24:00)' — nothing before or after.</t>
+  </si>
+  <si>
+    <t>At SPM42 Plain Room the line under the slots read 'No setup or turnaround needed at this venue.' both before and after ticking Night, and no Setup or Turnaround line appeared. The request reads '10 Mar 2027 · PM, Night (13:00-24:00) · Classroom', Pending. Venue Staff's row for it carries no Setup or Turnaround line either.</t>
   </si>
   <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones). Run this case before TC09, so Day 2 has no request yet.
@@ -623,6 +690,12 @@
     <t>Attempts 1 and 2 show 'The chosen slots do not cover the session's time (2 Mar 2027, 14:00–17:00).'
 Attempt 3 shows 'The chosen slots do not cover the event's time (7 Mar 2027, 09:00–17:00).'
 No request is created.</t>
+  </si>
+  <si>
+    <t>Attempt 1 (Day 2, AM only): 'The chosen slots do not cover the session's time (2 Mar 2027, 14:00-17:00).' Attempt 2 (Day 2, moved to 1 Mar, PM): the same message, still naming the session's own date. Attempt 3 (SPM42 Refusal Checks, an event with no sessions, AM only): 'The chosen slots do not cover the event's time (7 Mar 2027, 09:00-17:00).' No request was created by any attempt.</t>
+  </si>
+  <si>
+    <t>Attempt 2 is the useful one: the refusal names the session's time even though the date was changed to another session's, so the check is against the chosen session rather than whatever date is in the box.</t>
   </si>
   <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones).
@@ -654,6 +727,12 @@
 Three separate requests are listed, each labelled with its session and showing that session's layout: Day 1 Theatre, Day 2 Classroom, Day 3 Banquet.</t>
   </si>
   <si>
+    <t>Each session opened on its own date with its own slot already ticked - Day 1: 1 Mar 2027 AM; Day 2: 2 Mar 2027 PM; Day 3: 3 Mar 2027 Night - and each at its own venue. Three separate requests are listed, each labelled with its session and its own layout: '1 Mar 2027 · AM (07:00-12:00) · Theatre', '2 Mar 2027 · PM (13:00-18:00) · Classroom', '3 Mar 2027 · Night (19:00-24:00) · Banquet'. All three Pending.</t>
+  </si>
+  <si>
+    <t>Each session's layout differs from the others, which is what shows the request uses the session's own requirements rather than the event's.</t>
+  </si>
+  <si>
     <t>TC04 and TC09 have been run.
 Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).</t>
   </si>
@@ -671,6 +750,9 @@
     <t>The 6 Mar request shows the event reference (EVT-…) and title 'SPM42 Town Hall', with no session.
 The 2 Mar request shows 'SPM42 Three-Session Forum' and session 'Day 2'.
 Clicking an event reference opens that event.</t>
+  </si>
+  <si>
+    <t>On Marcus Wong's Booking Requests screen the Town Hall row reads 'EVT-000759 | SPM42 Town Hall | Orchard Seminar Room (ORC-SEM) | 6 Mar 2027 · AM, PM (07:00-18:00)' with no session named. The Three-Session row reads 'EVT-000765 | SPM42 Three-Session Forum | Session: Day 2 | Orchard Studio (ORC-STU) | 2 Mar 2027 · PM (13:00-18:00)'. Event references are rendered as links to the event.</t>
   </si>
   <si>
     <t>TC04 has been run.</t>
@@ -691,6 +773,9 @@
   <si>
     <t>Both screens show the request with the status badge 'Pending'.
 Marcus Wong's row shows Orchard Seminar Room, '6 Mar 2027 · AM, PM (07:00–18:00)', 'Setup: 5 Mar 2027 Night (19:00–24:00)', 'Turnaround: 6 Mar 2027 Night (19:00–24:00)', and Requested by Daniel Tan.</t>
+  </si>
+  <si>
+    <t>The Venue Staff row shows 'Orchard Seminar Room (ORC-SEM) | 6 Mar 2027 · AM, PM (07:00-18:00) | Setup: 5 Mar 2027 Night (19:00-24:00) | Turnaround: 6 Mar 2027 Night (19:00-24:00) | Layout: Theatre | Daniel Tan | Pending'. The Coordinator's own Venue tab shows the same request with the status badge Pending.</t>
   </si>
   <si>
     <t>Seeded data: 'Town Hall Q4' (status Planning) is assigned to Daniel Tan.
@@ -715,6 +800,12 @@
 Priya Raj's Venue tab says 'Only the assigned Coordinator can request a venue booking.'</t>
   </si>
   <si>
+    <t>None of the five accounts saw a Request booking button anywhere for the event. Priya Raj (a Coordinator who is not the assigned one), Grace Lim and Marcus Wong each saw 'Only the assigned Coordinator can request a venue booking.' Rachel Ng and Kenji Sato have no Venue tab for the event at all, so the question never arises for them.</t>
+  </si>
+  <si>
+    <t>The refusal is shown to roles that can open the Venue tab; the Organiser and Technical Support are stopped a step earlier by not being offered the tab. Both outcomes satisfy the criterion - no button for any of the five.</t>
+  </si>
+  <si>
     <t>Seeded data.
 Logged in as Coordinator Joel Fernandez (joel.fernandez@connectsphere.com / password123), assigned to 'Pearl Delta Supplier Forum' (status Cancelled, 29 Oct 2026 (2026-09-26 + 33) 09:00-14:00).</t>
   </si>
@@ -731,6 +822,9 @@
   <si>
     <t>No 'Request booking' button is shown.
 The page says 'A venue cannot be requested for a completed, cancelled or rejected event.'</t>
+  </si>
+  <si>
+    <t>On the cancelled event's Venue tab the page read 'A venue cannot be requested for a completed, cancelled or rejected event.' and no Request booking button was present on any venue card.</t>
   </si>
   <si>
     <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones). Seeded data, unchanged:
@@ -769,6 +863,12 @@
 No request is created for any of the three.</t>
   </si>
   <si>
+    <t>1. SPM42 Clash Check at Marina Auditorium, 21 Oct 2026: 'Marina Auditorium is already booked for this time.' 2. Staff Retreat at Changi Conference Centre, 14 Dec 2026: 'Changi Conference Centre is on hold for another event at this time.' 3. Sports Meet at Marina Auditorium, 20 Nov 2026: 'Marina Auditorium is unavailable at this time.' No request was created in any of the three.</t>
+  </si>
+  <si>
+    <t>The three refusals are worded differently from each other, so a tester can tell an approved booking from a pending hold from a maintenance period without leaving the screen.</t>
+  </si>
+  <si>
     <t>Seeded data: 'Product Showcase' has an Approved booking at Marina Auditorium (MAR-AUD, setup 60 min, teardown 30 min) on 21 Oct 2026 AM + PM, so its setup holds 20 Oct 2026 Night.
 Logged in as Daniel Tan, assigned to 'Keynote Rehearsal' (status Planning, 20 Oct 2026 (2026-09-26 + 24) 14:00-16:00, no sessions).</t>
   </si>
@@ -790,41 +890,16 @@
 No request is created.</t>
   </si>
   <si>
-    <t>npm run fixtures:spm42 has been run once at the start of this test pass (do not re-run it between cases - later cases use requests made in earlier ones). It creates:
-- 'SPM42 Cancelled Hold' with a Cancelled booking at Orchard Gallery (ORC-GAL), 15 Mar 2027 (2026-09-26 + 170) 09:00-17:00.
-- 'SPM42 Rejected Hold' with a Rejected booking at Marina Auditorium (MAR-AUD), 16 Mar 2027 (2026-09-26 + 171) 09:00-18:00 — had it been approved, its turnaround would hold 16 Mar Night.
-Logged in as Daniel Tan, assigned to the two events in Test data (status Planning, no sessions).</t>
-  </si>
-  <si>
-    <t>1. Log in as daniel.tan@connectsphere.com / password123
-2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
-3. Click 'SPM42 After Cancellation' in the list
-4. Click the 'Venue' tab
-5. Find 'Orchard Gallery (ORC-GAL)' in the venue list and click its 'Request booking' button
-6. Make sure 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked for 15 Mar 2027, click 'Submit request' and read the message
-7. Click 'Back to Venue' and read the status under 'Booking requests'
-8. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
-9. Click 'SPM42 After Rejection' in the list
-10. Click the 'Venue' tab
-11. Find 'Marina Auditorium (MAR-AUD)' in the venue list and click its 'Request booking' button
-12. Make sure 'AM (07:00–12:00)' and 'PM (13:00–18:00)' are ticked for 17 Mar 2027, click 'Submit request' and read the message
-13. Click 'Back to Venue' and read the status under 'Booking requests'</t>
-  </si>
-  <si>
-    <t>1. spm42_after_cancel 'SPM42 After Cancellation', 15 Mar 2027 10:00-16:00, Orchard Gallery (same slots as the cancelled booking)
-2. spm42_after_reject 'SPM42 After Rejection', 17 Mar 2027 (2026-09-26 + 172) 10:00-16:00, Marina Auditorium (its setup takes 16 Mar Night)</t>
-  </si>
-  <si>
-    <t>Both show 'Booking request sent to Venue Staff.' and the request is Pending.</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Sammi</t>
+    <t>Requesting Marina Auditorium for 20 Oct 2026 PM was refused with 'Marina Auditorium is already booked for this time.', although the two events' own slots (20 Oct PM and 21 Oct AM + PM) do not overlap - the clash is only through 20 Oct Night, which this request's turnaround and the existing booking's setup both need. No request was created.</t>
+  </si>
+  <si>
+    <t>This is the case that proves setup and turnaround slots are held against other bookings, not merely displayed on the calendar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAN JORDAN </t>
+  </si>
+  <si>
+    <t>TAN JORDAN</t>
   </si>
 </sst>
 </file>
@@ -834,7 +909,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -871,6 +946,12 @@
       <u/>
       <sz val="10"/>
       <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -966,7 +1047,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -991,6 +1072,9 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1216,7 +1300,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1226,495 +1310,495 @@
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="3" spans="1:6" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="3" spans="1:6" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="C3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="C19" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="16"/>
+    </row>
+    <row r="23" spans="1:6" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="9" t="s">
+      <c r="B23" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="16"/>
+    </row>
+    <row r="24" spans="1:6" ht="125.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="13" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="B24" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="16"/>
+    </row>
+    <row r="25" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="16"/>
+    </row>
+    <row r="26" spans="1:6" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="16"/>
+    </row>
+    <row r="27" spans="1:6" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="16" t="s">
+      <c r="B27" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="16"/>
+    </row>
+    <row r="28" spans="1:6" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="16"/>
+    </row>
+    <row r="29" spans="1:6" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="16"/>
+    </row>
+    <row r="30" spans="1:6" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="15"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="15"/>
-    </row>
-    <row r="23" spans="1:6" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="15"/>
-    </row>
-    <row r="24" spans="1:6" ht="125.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" s="15"/>
-    </row>
-    <row r="25" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" s="15"/>
-    </row>
-    <row r="26" spans="1:6" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="15"/>
-    </row>
-    <row r="27" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="15"/>
-    </row>
-    <row r="28" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" s="15"/>
-    </row>
-    <row r="29" spans="1:6" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" s="15"/>
-    </row>
-    <row r="30" spans="1:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="15"/>
-    </row>
-    <row r="32" spans="1:6" ht="166" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="16"/>
+    </row>
+    <row r="32" spans="1:6" ht="166.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="15"/>
+        <v>118</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1766,119 +1850,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="125.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="287.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="287.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -1892,119 +2022,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="98.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="62.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -2018,119 +2194,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="152.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="152.55000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="62.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="12">
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -2144,119 +2366,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="260.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="260.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -2270,119 +2538,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="98.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -2396,119 +2710,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="166.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="166" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="382" customHeight="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="382.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="62.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -2522,119 +2882,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="139.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -2648,119 +3054,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="166.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="166" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="314.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="314.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -2774,119 +3226,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="125.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B3" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="260.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="260.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="98.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>105</v>
-      </c>
       <c r="B6" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="139.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -2900,119 +3398,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -3026,119 +3570,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="247" customHeight="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="247.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="62.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -3152,119 +3742,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="193" customHeight="1" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="193.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="62.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -3278,119 +3914,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="206.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="206.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -3404,119 +4086,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="382" customHeight="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="382.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="98.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="139.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -3530,119 +4258,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="193" customHeight="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="193.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="62.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>
@@ -3656,119 +4430,165 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="287.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="287.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="62.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B15" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12">
         <v>46296</v>
       </c>
     </row>

--- a/docs/test-cases/SPM-42_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-42_Test_Cases.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -79,6 +79,9 @@
       <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="5">
@@ -192,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,6 +236,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1113,11 +1119,15 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H15" s="14" t="n"/>
-      <c r="I15" s="14" t="n"/>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="25.05" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -1292,6 +1302,7 @@
       </c>
     </row>
     <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="13.05" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
@@ -1491,6 +1502,7 @@
       </c>
       <c r="F30" s="16" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="166.05" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
@@ -4957,53 +4969,60 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.796875" customWidth="1" min="1" max="1"/>
     <col width="56.796875" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.05" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.55" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.55" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-42-TC12</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="112.05" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>SPM-42-TC12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="260.55" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Seeded data: 'Town Hall Q4' (status Planning) is assigned to Daniel Tan.
 Accounts (password123): Coordinator Priya Raj (priya.raj@connectsphere.com), Organiser Rachel Ng (rachel.ng@meridianfina.com, organiser of 'Town Hall Q4'), Ops Manager Grace Lim (grace.lim@connectsphere.com), Venue Staff Marcus Wong (marcus.wong@connectsphere.com), Technical Support Kenji Sato (kenji.sato@connectsphere.com).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="260.55" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="5" ht="44.55" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1. Log in as priya.raj@connectsphere.com / password123
 2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
@@ -5017,188 +5036,193 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44.55" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Accounts: Priya Raj (Coordinator, not assigned), Rachel Ng (Organiser), Grace Lim (Ops Manager), Marcus Wong (Venue Staff), Kenji Sato (Technical Support)</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="58.05" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Accounts: Priya Raj (Coordinator, not assigned), Rachel Ng (Organiser), Grace Lim (Ops Manager), Marcus Wong (Venue Staff), Kenji Sato (Technical Support)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.55" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>None of the five sees a 'Request booking' button anywhere for this event.
 Priya Raj's Venue tab says 'Only the assigned Coordinator can request a venue booking.'</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.55" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="12.5" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B9" s="12" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" ht="13.05" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="13.05" customHeight="1"/>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="12.5" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>None of the five sees a 'Request booking' button anywhere for this event.
 Priya Raj's Venue tab says 'Only the assigned Coordinator can request a venue booking.'</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="12.5" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sammi</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B16" s="12" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="17" ht="13.05" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="13.05" customHeight="1"/>
+    <row r="18" ht="85.05" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="85.05" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>None of the five accounts saw a Request booking button anywhere for the event. Priya Raj (a Coordinator who is not the assigned one), Grace Lim and Marcus Wong each saw 'Only the assigned Coordinator can request a venue booking.' Rachel Ng and Kenji Sato have no Venue tab for the event at all, so the question never arises for them.</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="n"/>
     </row>
     <row r="19" ht="17.55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>None of the five accounts saw a Request booking button anywhere for the event. Priya Raj (a Coordinator who is not the assigned one), Grace Lim and Marcus Wong each saw 'Only the assigned Coordinator can request a venue booking.' Rachel Ng and Kenji Sato have no Venue tab for the event at all, so the question never arises for them.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58.05" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>The refusal is shown to roles that can open the Venue tab; the Organiser and Technical Support are stopped a step earlier by not being offered the tab. Both outcomes satisfy the criterion - no button for any of the five.</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="17.55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAN JORDAN </t>
+          <t>The refusal is shown to roles that can open the Venue tab; the Organiser and Technical Support are stopped a step earlier by not being offered the tab. Both outcomes satisfy the criterion - no button for any of the five.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAN JORDAN </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B23" s="12" t="n">
         <v>46296</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/test-cases/SPM-42_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-42_Test_Cases.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -82,6 +82,10 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -195,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -239,6 +243,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1162,11 +1169,15 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>#103</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="25.05" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -1301,8 +1312,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="13.05" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
@@ -1502,7 +1511,6 @@
       </c>
       <c r="F30" s="16" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="166.05" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
@@ -5233,53 +5241,61 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.796875" customWidth="1" min="1" max="1"/>
     <col width="56.796875" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.05" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="64" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-23): The page now reads 'A venue cannot be requested for a completed, cancelled, rejected or withdrawn event.' instead of 'A venue cannot be requested for a completed, cancelled or rejected event.' (SPM-59, discussion #103: the messages that refuse an action on a closed event now name withdrawn events too). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13.05" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.55" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="17.55" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>SPM-42-TC13</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="71.55" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+    <row r="4" ht="71.55" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Seeded data.
 Logged in as Coordinator Joel Fernandez (joel.fernandez@connectsphere.com / password123), assigned to 'Pearl Delta Supplier Forum' (status Cancelled, 29 Oct 2026 (2026-09-26 + 33) 09:00-14:00).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="98.55" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="5" ht="98.55" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1. Log in as joel.fernandez@connectsphere.com / password123
 2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
@@ -5289,188 +5305,193 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="17.55" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="6" ht="17.55" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Event status: Cancelled</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="44.55" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="7" ht="44.55" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>No 'Request booking' button is shown.
 The page says 'A venue cannot be requested for a completed, cancelled or rejected event.'</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.55" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="8" ht="17.55" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="12.5" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="9" ht="12.5" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B9" s="12" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="10" ht="13.05" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10"/>
+    <row r="11" ht="13.05" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="37.5" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="37.5" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>No 'Request booking' button is shown.
 The page says 'A venue cannot be requested for a completed, cancelled or rejected event.'</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="12.5" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sammi</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="12.5" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B16" s="12" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="17" ht="13.05" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17"/>
+    <row r="18" ht="13.05" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="58.05" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="58.05" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>On the cancelled event's Venue tab the page read 'A venue cannot be requested for a completed, cancelled or rejected event.' and no Request booking button was present on any venue card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="17.55" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17.55" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="17.55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17.55" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">TAN JORDAN </t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B23" s="12" t="n">
         <v>46296</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/test-cases/SPM-42_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-42_Test_Cases.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -82,10 +82,6 @@
     </font>
     <font>
       <color rgb="FF000000"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -199,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -243,9 +239,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1169,15 +1162,11 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>#103</t>
-        </is>
-      </c>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="25.05" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -1312,6 +1301,8 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="13.05" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
@@ -1511,6 +1502,7 @@
       </c>
       <c r="F30" s="16" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="166.05" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
@@ -5241,61 +5233,53 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.796875" customWidth="1" min="1" max="1"/>
     <col width="56.796875" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="64" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>v2 (2026-10-23): The page now reads 'A venue cannot be requested for a completed, cancelled, rejected or withdrawn event.' instead of 'A venue cannot be requested for a completed, cancelled or rejected event.' (SPM-59, discussion #103: the messages that refuse an action on a closed event now name withdrawn events too). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="13.05" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="1" ht="13.05" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="17.55" customHeight="1">
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.55" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>SPM-42-TC13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.55" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>Pre-conditions</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>SPM-42-TC13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.55" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Seeded data.
 Logged in as Coordinator Joel Fernandez (joel.fernandez@connectsphere.com / password123), assigned to 'Pearl Delta Supplier Forum' (status Cancelled, 29 Oct 2026 (2026-09-26 + 33) 09:00-14:00).</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="98.55" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="4" ht="98.55" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>1. Log in as joel.fernandez@connectsphere.com / password123
 2. Click 'All Events' in the sidebar (the list has no search box - use Ctrl+F to find the event)
@@ -5305,193 +5289,188 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="17.55" customHeight="1">
+    <row r="5" ht="17.55" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Event status: Cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.55" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Expected Result</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Event status: Cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44.55" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>No 'Request booking' button is shown.
 The page says 'A venue cannot be requested for a completed, cancelled or rejected event.'</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="17.55" customHeight="1">
+    <row r="7" ht="17.55" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.5" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="12.5" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B8" s="12" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11" ht="13.05" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="10" ht="13.05" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="37.5" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="37.5" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>No 'Request booking' button is shown.
 The page says 'A venue cannot be requested for a completed, cancelled or rejected event.'</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="12.5" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Executed by</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Sammi</t>
         </is>
       </c>
     </row>
     <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Sammi</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="12.5" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B15" s="12" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18" ht="13.05" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="17" ht="13.05" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="58.05" customHeight="1">
+      <c r="B17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="58.05" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>On the cancelled event's Venue tab the page read 'A venue cannot be requested for a completed, cancelled or rejected event.' and no Request booking button was present on any venue card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17.55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>On the cancelled event's Venue tab the page read 'A venue cannot be requested for a completed, cancelled or rejected event.' and no Request booking button was present on any venue card.</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17.55" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="21" ht="17.55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Executed by</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="17.55" customHeight="1">
+          <t xml:space="preserve">TAN JORDAN </t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAN JORDAN </t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B22" s="12" t="n">
         <v>46296</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
